--- a/20_项目/02_光与朽项目/06_发行追踪/游戏发行追踪.xlsx
+++ b/20_项目/02_光与朽项目/06_发行追踪/游戏发行追踪.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20328" windowHeight="10728"/>
+    <workbookView windowWidth="23688" windowHeight="13068"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
     <t>沅姗</t>
   </si>
   <si>
-    <t>结论：不推荐。表现力：怪物的种类丰富单动作单一，射线也缺乏更直观感受的变化。上手：肉鸽词条稀有度的辨识效果良好，阅读量小，玩家抉择和上手的压力小。核心体验：控制射线击败怪物，升级后可选择肉鸽词条进行强化，能对射线本身产生较大影响。成长追求：暂无。玩法：目前仅有主线推关一种玩法。付费：暂无。 总结：该产品为肉鸽塔防类，战斗中玩家需要保持极高的专注度，产品当前版本并不支持自动战斗，即使用手操作也存在一定的数值压力，玩家手操的付出缺乏对应的正反馈机制，虽然目前怪物的机制多元但词条之间缺乏联动性，再加上单场战斗时间过长会导致玩家出现厌恶感，故综上所述该产品不推荐。</t>
+    <t>结论：不推荐。表现力：怪物的种类丰富但动作单一，射线也缺乏更直观感受的变化。上手：肉鸽词条稀有度的辨识效果良好，阅读量小，玩家抉择和上手的压力小。核心体验：控制射线击败怪物，升级后可选择肉鸽词条进行强化，能对射线本身产生较大影响。成长追求：暂无。玩法：目前仅有主线推关一种玩法。付费：暂无。 总结：该产品为肉鸽塔防类，战斗中玩家需要保持极高的专注度，产品当前版本并不支持自动战斗，即使用手操作也存在一定的数值压力，玩家手操的付出缺乏对应的正反馈机制，虽然目前怪物的机制多元但词条之间缺乏联动性，再加上单场战斗时间过长会导致玩家出现厌恶感，故综上所述该产品不推荐。</t>
   </si>
   <si>
     <t>广州趣城网络科技有限公司</t>
